--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icf-1:Body functions (chapter b) take only the extent-of-impairment qualifier. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('b') implies component.where(code.coding.code != 'extent-of-impairment').empty()}mii-icf-2:Body structures (chapter s) take only extent, nature of change and anatomical location. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('s') implies component.where(code.coding.code.subsetOf('extent-of-impairment-structure' | 'nature-of-change' | 'anatomical-location').not()).empty()}mii-icf-3:Activities and participation (chapter d) take only capacity and performance. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('d') implies component.where(code.coding.code.subsetOf('capacity' | 'performance').not()).empty()}mii-icf-4:Environmental factors (chapter e) take only the barrier or facilitator qualifier. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('e') implies component.where(code.coding.code.subsetOf('barrier' | 'facilitator').not()).empty()}mii-icf-5:An environmental factor is graded as a barrier or as a facilitator, not as both at once. {component.where(code.coding.code = 'barrier').empty() or component.where(code.coding.code = 'facilitator').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icf-1:Body functions (chapter b) take only the extent-of-impairment qualifier. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('b') implies component.where(code.coding.code != 'extent-of-impairment').empty()}mii-icf-2:Body structures (chapter s) take only extent, nature of change and anatomical location. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('s') implies component.where(code.coding.code != 'extent-of-impairment-structure' and code.coding.code != 'nature-of-change' and code.coding.code != 'anatomical-location').empty()}mii-icf-3:Activities and participation (chapter d) take only capacity and performance. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('d') implies component.where(code.coding.code != 'capacity' and code.coding.code != 'performance').empty()}mii-icf-4:Environmental factors (chapter e) take only the barrier or facilitator qualifier. {code.coding.where(system='http://hl7.org/fhir/sid/icf').code.first().startsWith('e') implies component.where(code.coding.code != 'barrier' and code.coding.code != 'facilitator').empty()}mii-icf-5:An environmental factor is graded as a barrier or as a facilitator, not as both at once. {component.where(code.coding.code = 'barrier').empty() or component.where(code.coding.code = 'facilitator').empty()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-icf-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
